--- a/examples/SmallDrugCombo_Zhou_CellChemBio_2026/tables/data__sa_fit_heat_GR__GR_Max.xlsx
+++ b/examples/SmallDrugCombo_Zhou_CellChemBio_2026/tables/data__sa_fit_heat_GR__GR_Max.xlsx
@@ -381,65 +381,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCF-7</t>
+          <t>CAMA-1</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.3378625</v>
+        <v>0.5859875</v>
       </c>
       <c r="C2">
-        <v>0.3657</v>
+        <v>0.2246</v>
       </c>
       <c r="D2">
-        <v>0.38975</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-47D</t>
+          <t>EFM-19</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.6278250000000001</v>
+        <v>0.6691374999999999</v>
       </c>
       <c r="C3">
-        <v>0.763225</v>
+        <v>0.47085</v>
       </c>
       <c r="D3">
-        <v>0.2051999999999999</v>
+        <v>-0.273575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAMA-1</t>
+          <t>MCF-7</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.5859875</v>
+        <v>0.3378625</v>
       </c>
       <c r="C4">
-        <v>0.2246</v>
+        <v>0.3657</v>
       </c>
       <c r="D4">
-        <v>1.1</v>
+        <v>0.38975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFM-19</t>
+          <t>T-47D</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.6691374999999999</v>
+        <v>0.6278250000000001</v>
       </c>
       <c r="C5">
-        <v>0.47085</v>
+        <v>0.763225</v>
       </c>
       <c r="D5">
-        <v>-0.273575</v>
+        <v>0.2051999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCF-7</t>
+          <t>CAMA-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-47D</t>
+          <t>EFM-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAMA-1</t>
+          <t>MCF-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFM-19</t>
+          <t>T-47D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
